--- a/data_dictionaries/es/Belvo_Data_Dictionary_es.xlsx
+++ b/data_dictionaries/es/Belvo_Data_Dictionary_es.xlsx
@@ -31570,7 +31570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I123"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -32121,17 +32121,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>tax_details.retained_taxes[].tax</t>
+          <t>tax_details.retained_taxes[].tax_type</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>El tipo de impuesto retenido (por ejemplo, ISR, IVA o IEPS).</t>
+          <t>El código de tipo de impuesto para este impuesto retenido, según lo definido por la entidad legal en el país.</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>Tasa</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -32147,7 +32147,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -32156,25 +32156,25 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>tax_details.retained_taxes[].tax_percentage</t>
+          <t>tax_details.retained_taxes[].tax</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>El porcentaje de impuesto retenido.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
+          <t>El tipo de impuesto retenido (por ejemplo, ISR, IVA o IEPS).</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>ISR</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -32182,7 +32182,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -32191,12 +32191,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>tax_details.retained_taxes[].pre_tax_amount</t>
+          <t>tax_details.retained_taxes[].tax_percentage</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>El monto antes de impuestos.</t>
+          <t>El porcentaje de impuesto retenido.</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
@@ -32226,19 +32226,15 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>tax_details.retained_taxes[].tax_amount</t>
+          <t>tax_details.retained_taxes[].pre_tax_amount</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>El monto del impuesto retenido.</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
+          <t>El monto antes de impuestos.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
           <t>number</t>
@@ -32256,7 +32252,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -32265,21 +32261,29 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>tax_details.transferred_taxes</t>
+          <t>tax_details.retained_taxes[].tax_amount</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Lista de impuestos transferidos.</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr"/>
+          <t>El monto del impuesto retenido.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -32296,22 +32300,18 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>tax_details.transferred_taxes[].tax</t>
+          <t>tax_details.transferred_taxes</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>El tipo de impuesto transferido (por ejemplo, ISR, IVA o IEPS).</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>IVA</t>
-        </is>
-      </c>
+          <t>Lista de impuestos transferidos.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -32331,29 +32331,25 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>tax_details.transferred_taxes[].tax_percentage</t>
+          <t>tax_details.transferred_taxes[].tax_type</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>El porcentaje de impuesto transferido.</t>
+          <t>El código del tipo de impuesto (TipoFactor) para este impuesto trasladado, según lo definido por la entidad legal en el país.</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Tasa</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -32361,7 +32357,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -32370,29 +32366,25 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>tax_details.transferred_taxes[].pre_tax_amount</t>
+          <t>tax_details.transferred_taxes[].tax</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>El monto antes de impuestos.</t>
+          <t>El tipo de impuesto transferido (por ejemplo, ISR, IVA o IEPS).</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>IVA</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -32409,17 +32401,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>tax_details.transferred_taxes[].tax_amount</t>
+          <t>tax_details.transferred_taxes[].tax_percentage</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>El monto del impuesto transferido.</t>
+          <t>El porcentaje de impuesto transferido.</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>150.4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -32448,33 +32440,37 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>sender_id</t>
+          <t>tax_details.transferred_taxes[].pre_tax_amount</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>El ID fiscal del remitente de la factura</t>
+          <t>El monto antes de impuestos.</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>AAA111111AA11</t>
+          <t>940</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -32483,25 +32479,29 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>sender_fiscal_regime</t>
+          <t>tax_details.transferred_taxes[].tax_amount</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>El régimen fiscal del remitente, según lo definido por la entidad legal en el país.</t>
+          <t>El monto del impuesto transferido.</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>150.4</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -32509,7 +32509,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -32518,17 +32518,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>sender_name</t>
+          <t>sender_id</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>El nombre del remitente de la factura.</t>
+          <t>El ID fiscal del remitente de la factura</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>ACME CORP</t>
+          <t>AAA111111AA11</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -32553,10 +32553,80 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>sender_fiscal_regime</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>El régimen fiscal del remitente, según lo definido por la entidad legal en el país.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>sender_name</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>El nombre del remitente de la factura.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>ACME CORP</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>sender_tax_fraud_status</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Indica si el remitente está o no en la lista de fraude fiscal del SAT por haber presentado datos incorrectos, tener pagos pendientes o haber realizado negocios que violan las regulaciones de la institución fiscal.&lt;br&gt;&lt;br&gt;
 El SAT actualiza la lista de fraude fiscal cada tres meses. &lt;br&gt;&lt;br&gt;
@@ -32579,79 +32649,9 @@
 El receptor o remitente no se encuentra en la lista (en otras palabras, están cumpliendo con las regulaciones de la institución fiscal).</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>NO_TAX_FRAUD_STATUS</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>receiver_id</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>El ID fiscal del receptor de la factura.</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>BBB222222BB22</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>receiver_postal_code</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>El código postal del receptor.</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>11560</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -32676,17 +32676,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>receiver_fiscal_regime</t>
+          <t>receiver_id</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>El régimen fiscal del receptor, según lo definido por la entidad legal en el país.</t>
+          <t>El ID fiscal del receptor de la factura.</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>BBB222222BB22</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -32697,7 +32697,7 @@
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -32711,17 +32711,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>receiver_name</t>
+          <t>receiver_postal_code</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>El nombre del receptor de la factura.</t>
+          <t>El código postal del receptor.</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>BELVO CORP</t>
+          <t>11560</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -32732,12 +32732,12 @@
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -32746,10 +32746,80 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>receiver_fiscal_regime</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>El régimen fiscal del receptor, según lo definido por la entidad legal en el país.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>receiver_name</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>El nombre del receptor de la factura.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>BELVO CORP</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
           <t>receiver_tax_fraud_status</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Indica si el receptor está o no en la lista de fraude fiscal del SAT por haber presentado datos incorrectos, tener pagos pendientes o haber realizado negocios que violan las regulaciones de la institución fiscal.&lt;br&gt;&lt;br&gt;
 El SAT actualiza la lista de fraude fiscal cada tres meses. &lt;br&gt;&lt;br&gt;
@@ -32772,90 +32842,20 @@
 El receptor o emisor no se encuentra en la lista (en otras palabras, está cumpliendo con las regulaciones de la institución fiscal).</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>NO_TAX_FRAUD_STATUS</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>cancelation_status</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Si la factura es cancelada, este campo indica el estado de la cancelación.</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr"/>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>cancelation_update_date</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>La fecha de la cancelación de la factura, en formato `YYYY-MM-DD`.</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>2019-12-02</t>
-        </is>
-      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -32869,29 +32869,21 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>certification_date</t>
+          <t>cancelation_status</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>La fecha de la certificación fiscal, en formato `YYYY-MM-DD`.</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>2019-12-01</t>
-        </is>
-      </c>
+          <t>Si la factura es cancelada, este campo indica el estado de la cancelación.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
+      <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -32908,17 +32900,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>certification_authority</t>
+          <t>cancelation_update_date</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>El ID fiscal del proveedor de certificación.</t>
+          <t>La fecha de la cancelación de la factura, en formato `YYYY-MM-DD`.</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>CCC333333CC33</t>
+          <t>2019-12-02</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -32926,7 +32918,11 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -32943,227 +32939,231 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>certification_date</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>La fecha de la certificación fiscal, en formato `YYYY-MM-DD`.</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>2019-12-01</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>certification_authority</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>El ID fiscal del proveedor de certificación.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>CCC333333CC33</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>payment_type</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>El código de tipo de pago utilizado para esta factura, según lo definido por la entidad legal del país.
 - 🇲🇽 México &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payment-type" target="_blank"&gt;Artículo de referencia del catálogo SAT&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>payment_type_description</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>*Este campo ha quedado obsoleto. Para obtener más información sobre Belvo y la obsolescencia, consulte nuestra explicación de Campos obsoletos.*</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>payment_method</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>El código del método de pago utilizado para esta factura, según lo definido por la entidad legal del país.
 - 🇲🇽 México &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payment-method" target="_blank"&gt;artículo de referencia del catálogo SAT&lt;/a&gt;. Para México, devolvemos `PUE`, `PPD` o `null`.</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>PUE</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>PUE, PPD, None</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>payment_method_description</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>*Este campo ha sido desaprobado. Para obtener más información sobre Belvo y la desaprobación, consulte nuestra explicación de Campos desaprobados.*
 *La descripción del método de pago utilizado para esta factura.*</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>usage</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>El código de uso de la factura, tal como lo define la entidad legal del país.
 - 🇲🇽 México &lt;a href="https://developers.belvo.com/docs/sat-catalogs#usage" target="_blank"&gt;Artículo de referencia del catálogo del SAT&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>P01</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>La versión CFDI de la factura.</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>place_of_issue</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>El código postal de donde se emitió la factura.</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>01165</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -33188,29 +33188,33 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>invoice_details</t>
+          <t>version</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Una lista de descripciones para cada artículo (producto comprado o servicio prestado) en la factura.</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
+          <t>La versión CFDI de la factura.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -33219,17 +33223,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].collected_at</t>
+          <t>place_of_issue</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>La marca de tiempo ISO-8601 cuando se recopiló el punto de datos.</t>
+          <t>El código postal de donde se emitió la factura.</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2022-02-09T08:45:50.406032Z</t>
+          <t>01165</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -33237,11 +33241,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>date-time</t>
-        </is>
-      </c>
+      <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -33249,7 +33249,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -33258,22 +33258,18 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].description</t>
+          <t>invoice_details</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>La descripción del artículo de la factura (una factura puede tener uno o más artículos).</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>December 2019 accounting fees</t>
-        </is>
-      </c>
+          <t>Una lista de descripciones para cada artículo (producto comprado o servicio prestado) en la factura.</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -33284,7 +33280,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -33293,17 +33289,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].product_identification</t>
+          <t>invoice_details[].collected_at</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>El código de identificación del producto o del servicio, tal como lo define la entidad legal en el país.\n- \U0001F1F2\U0001F1FD &lt;a href="http://200.57.3.89/Pys/catPyS.aspx" target="_blank"&gt;México&lt;/a&gt;.</t>
+          <t>La marca de tiempo ISO-8601 cuando se recopiló el punto de datos.</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>84101600</t>
+          <t>2022-02-09T08:45:50.406032Z</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -33311,15 +33307,19 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -33328,29 +33328,25 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].quantity</t>
+          <t>invoice_details[].description</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>La cantidad de este artículo de factura.</t>
+          <t>La descripción del artículo de la factura (una factura puede tener uno o más artículos).</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>December 2019 accounting fees</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -33367,17 +33363,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].unit_code</t>
+          <t>invoice_details[].product_identification</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>La unidad de medida, según lo definido por la entidad legal en el país. \n- \U0001F1F2\U0001F1FD México &lt;a href="https://developers.belvo.com/docs/sat-catalogs#unit-code" target="_blank"&gt;Referencia del catálogo SAT&lt;/a&gt;.</t>
+          <t>El código de identificación del producto o del servicio, tal como lo define la entidad legal en el país.\n- \U0001F1F2\U0001F1FD &lt;a href="http://200.57.3.89/Pys/catPyS.aspx" target="_blank"&gt;México&lt;/a&gt;.</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>E48</t>
+          <t>84101600</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -33402,25 +33398,29 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].unit_description</t>
+          <t>invoice_details[].quantity</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>La descripción del artículo, según lo definido por la entidad legal en el país.\n- \U0001F1F2\U0001F1FD México &lt;a href="https://developers.belvo.com/docs/sat-catalogs#unit-code" target="_blank"&gt;Referencia del catálogo SAT&lt;/a&gt;.</t>
+          <t>La cantidad de este artículo de factura.</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Unidad de servicio</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -33437,29 +33437,25 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].unit_amount</t>
+          <t>invoice_details[].unit_code</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>El precio de un artículo singular.</t>
+          <t>La unidad de medida, según lo definido por la entidad legal en el país. \n- \U0001F1F2\U0001F1FD México &lt;a href="https://developers.belvo.com/docs/sat-catalogs#unit-code" target="_blank"&gt;Referencia del catálogo SAT&lt;/a&gt;.</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>E48</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -33476,15 +33472,19 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].tax_type</t>
+          <t>invoice_details[].unit_description</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>El tipo de impuesto del artículo.</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr"/>
+          <t>La descripción del artículo, según lo definido por la entidad legal en el país.\n- \U0001F1F2\U0001F1FD México &lt;a href="https://developers.belvo.com/docs/sat-catalogs#unit-code" target="_blank"&gt;Referencia del catálogo SAT&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Unidad de servicio</t>
+        </is>
+      </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -33493,7 +33493,7 @@
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -33507,17 +33507,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].pre_tax_amount</t>
+          <t>invoice_details[].unit_amount</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>El precio total de este artículo antes de aplicar impuestos es (`quantity` x `unit_amount`).</t>
+          <t>El precio de un artículo singular.</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -33546,17 +33546,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].tax_percentage</t>
+          <t>invoice_details[].discount</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>El porcentaje de impuesto a aplicar.</t>
+          <t>El monto de descuento aplicado a este artículo de factura.</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -33571,7 +33571,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -33585,32 +33585,28 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].tax_amount</t>
+          <t>invoice_details[].tax_subject_code</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>El monto del impuesto para este artículo de factura (`pre_tax_amount` x `tax_percentage`).</t>
+          <t>Indica a qué impuesto está sujeto este artículo, según lo definido por la entidad legal en el país.</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -33624,32 +33620,28 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].total_amount</t>
+          <t>invoice_details[].identifier_number</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>El precio total para este artículo de factura (`pre_tax_amount` + `tax_amount`).</t>
+          <t>El número de identificación del artículo, tal como lo define el vendedor. Esto se puede utilizar para identificar el producto o servicio en el sistema del vendedor.</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>PROD-12345</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -33663,29 +33655,37 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].retained_taxes</t>
+          <t>invoice_details[].pre_tax_amount</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>El impuesto retenido en el artículo de la factura.</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr"/>
+          <t>El precio total de este artículo antes de aplicar impuestos es (`quantity` x `unit_amount`).</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -33694,37 +33694,37 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].retained_taxes[].collected_at</t>
+          <t>invoice_details[].tax_percentage</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>La marca de tiempo ISO-8601 cuando se recopiló el punto de datos.</t>
+          <t>El porcentaje de impuesto a aplicar.</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>2022-02-09T08:45:50.406032Z</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>date-time</t>
+          <t>float</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -33733,25 +33733,29 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].retained_taxes[].tax</t>
+          <t>invoice_details[].tax_amount</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>El tipo de impuesto retenido (por ejemplo, ISR, IVA o IEPS).</t>
+          <t>El monto del impuesto para este artículo de factura (`pre_tax_amount` x `tax_percentage`).</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -33768,17 +33772,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].retained_taxes[].tax_percentage</t>
+          <t>invoice_details[].total_amount</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>El porcentaje de impuesto retenido.</t>
+          <t>El precio total para este artículo de factura (`pre_tax_amount` + `tax_amount`).</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>464</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -33807,37 +33811,29 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].retained_taxes[].retained_tax_amount</t>
+          <t>invoice_details[].retained_taxes</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>El monto del impuesto retenido.</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>209.79</t>
-        </is>
-      </c>
+          <t>El impuesto retenido en el artículo de la factura.</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -33846,21 +33842,29 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].transferred_taxes</t>
+          <t>invoice_details[].retained_taxes[].collected_at</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Los impuestos transferidos relacionados con la factura.</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr"/>
+          <t>La marca de tiempo ISO-8601 cuando se recopiló el punto de datos.</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-09T08:45:50.406032Z</t>
+        </is>
+      </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -33877,17 +33881,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].transferred_taxes[].collected_at</t>
+          <t>invoice_details[].retained_taxes[].tax_type</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>La marca de tiempo ISO-8601 cuando se recopiló el punto de datos.</t>
+          <t>El código de tipo de impuesto para este impuesto retenido, según lo definido por la entidad legal en el país.</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>2022-02-09T08:45:50.406032Z</t>
+          <t>Tasa</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -33895,11 +33899,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>date-time</t>
-        </is>
-      </c>
+      <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -33916,17 +33916,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].transferred_taxes[].tax</t>
+          <t>invoice_details[].retained_taxes[].tax</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>El tipo de impuesto transferido (por ejemplo, ISR, IVA o IEPS).</t>
+          <t>El tipo de impuesto retenido (por ejemplo, ISR, IVA o IEPS).</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>IVA</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -33951,12 +33951,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].transferred_taxes[].tax_percentage</t>
+          <t>invoice_details[].retained_taxes[].tax_percentage</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>El porcentaje de impuesto transferido.</t>
+          <t>El porcentaje de impuesto retenido.</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -33990,12 +33990,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].transferred_taxes[].transferred_tax_amount</t>
+          <t>invoice_details[].retained_taxes[].retained_tax_amount</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>El monto del impuesto transferido.</t>
+          <t>El monto del impuesto retenido.</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -34029,10 +34029,228 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>invoice_details[].transferred_taxes</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Los impuestos transferidos relacionados con la factura.</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>invoice_details[].transferred_taxes[].collected_at</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>La marca de tiempo ISO-8601 cuando se recopiló el punto de datos.</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-09T08:45:50.406032Z</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>invoice_details[].transferred_taxes[].tax_type</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>El código de tipo de impuesto para este impuesto transferido, según lo definido por la entidad legal en el país.</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Tasa</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>invoice_details[].transferred_taxes[].tax</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>El tipo de impuesto transferido (por ejemplo, ISR, IVA o IEPS).</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>IVA</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>invoice_details[].transferred_taxes[].tax_percentage</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>El porcentaje de impuesto transferido.</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>invoice_details[].transferred_taxes[].transferred_tax_amount</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>El monto del impuesto transferido.</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>209.79</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>La moneda de la factura. Por ejemplo:
 - 🇧🇷 BRL (Real Brasileño)
@@ -34041,251 +34259,25 @@
 - 🇺🇸 USD (Dólar Estadounidense)</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>MXN</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>subtotal_amount</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>El monto antes de impuestos de esta factura (suma del `pre_tax_amount` de cada artículo).</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>exchange_rate</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>El tipo de cambio utilizado en esta factura para la moneda.</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>0.052</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>tax_amount</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>El monto del impuesto para esta factura (suma del `tax_amount` de cada artículo).</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>discount_amount</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>El monto total descontado en esta factura.</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>total_amount</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>El monto total de la factura (`subtotal_amount` + `tax_amount` - `discount_amount`)</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>454</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>related_invoices</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Una lista de facturas relacionadas.</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr"/>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -34294,28 +34286,32 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>related_invoices[].relationship_type</t>
+          <t>subtotal_amount</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>El tipo de relación entre esta factura y la factura relacionada, según lo definido por la entidad legal en el país. Para obtener más información, consulta nuestro &lt;a href="https://developers.belvo.com/docs/sat-catalogs#related-invoices" target="_blank"&gt;artículo de referencia del catálogo SAT&lt;/a&gt;.</t>
+          <t>El monto antes de impuestos de esta factura (suma del `pre_tax_amount` de cada artículo).</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -34329,28 +34325,32 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>related_invoices[].related_invoice_identification</t>
+          <t>exchange_rate</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>El SAT ID de la factura relacionada.</t>
+          <t>El tipo de cambio utilizado en esta factura para la moneda.</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>INV-123456</t>
+          <t>0.052</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -34364,21 +34364,29 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>tax_amount</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Una lista que detalla todos los pagos de facturas.</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr"/>
+          <t>El monto del impuesto para esta factura (suma del `tax_amount` de cada artículo).</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -34386,7 +34394,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -34395,27 +34403,27 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>payments[].date</t>
+          <t>discount_amount</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Marca de tiempo ISO-8601 cuando se realizó el pago.</t>
+          <t>El monto total descontado en esta factura.</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>2020-03-17T12:00:00.000Z</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>date-time</t>
+          <t>float</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -34434,46 +34442,256 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>El monto total de la factura (`subtotal_amount` + `tax_amount` - `discount_amount`)</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>related_invoices</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Una lista de facturas relacionadas.</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>related_invoices[].relationship_type</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>El tipo de relación entre esta factura y la factura relacionada, según lo definido por la entidad legal en el país. Para obtener más información, consulta nuestro &lt;a href="https://developers.belvo.com/docs/sat-catalogs#related-invoices" target="_blank"&gt;artículo de referencia del catálogo SAT&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>related_invoices[].related_invoice_identification</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>El SAT ID de la factura relacionada.</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>INV-123456</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>payments</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Una lista que detalla todos los pagos de facturas.</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>payments[].date</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Marca de tiempo ISO-8601 cuando se realizó el pago.</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>2020-03-17T12:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
           <t>payments[].payment_type</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Código de tipo de pago utilizado para esta factura, según lo definido por la entidad legal del país.
 - 🇲🇽 México &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payment-type" target="_blank"&gt;Artículo de referencia del catálogo SAT&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>payments[].currency</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>La moneda del pago. Por ejemplo:
 - 🇧🇷 BRL (Real Brasileño)
@@ -34482,223 +34700,9 @@
 Tenga en cuenta que pueden devolverse otras monedas además de las enumeradas anteriormente.</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>BRL</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>payments[].exchange_rate</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>La tasa de cambio de `currency` a MXN cuando se realizó el pago.</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>payments[].amount</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>El monto de la factura, en la moneda de la factura original.</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>8000.5</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>payments[].operation_number</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>El identificador interno de la institución fiscal para la operación.</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>831840</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>payments[].beneficiary_rfc</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>El ID fiscal del beneficiario del pago.</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>BNM840515VB1</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>payments[].beneficiary_account_number</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>El número de cuenta bancaria del beneficiario del pago.</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>12343453245633</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>payments[].payer_rfc</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>El ID fiscal del emisor del pago.</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>BKJM840515VB1</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -34723,17 +34727,17 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>payments[].payer_account_number</t>
+          <t>payments[].exchange_rate</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>El número de cuenta bancaria del emisor del pago.</t>
+          <t>La tasa de cambio de `currency` a MXN cuando se realizó el pago.</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>13343663245699</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -34758,25 +34762,29 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>payments[].payer_bank_name</t>
+          <t>payments[].amount</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>La institución bancaria que fue utilizada por el emisor del pago.</t>
+          <t>El monto de la factura, en la moneda de la factura original.</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>CITI BANAMEX</t>
+          <t>8000.5</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -34793,18 +34801,22 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>payments[].related_documents</t>
+          <t>payments[].operation_number</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Una lista de todas las facturas diferidas relacionadas afectadas por el pago.</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr"/>
+          <t>El identificador interno de la institución fiscal para la operación.</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>831840</t>
+        </is>
+      </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -34815,7 +34827,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
@@ -34824,17 +34836,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>payments[].related_documents[].invoice_identification</t>
+          <t>payments[].beneficiary_rfc</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>El ID único de la institución fiscal para la factura diferida relacionada.</t>
+          <t>El ID fiscal del beneficiario del pago.</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>7EE015F3-6311-11EA-B02A-00155D014007</t>
+          <t>BNM840515VB1</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -34845,7 +34857,7 @@
       <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -34859,10 +34871,216 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>payments[].beneficiary_account_number</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>El número de cuenta bancaria del beneficiario del pago.</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>12343453245633</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>payments[].payer_rfc</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>El ID fiscal del emisor del pago.</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>BKJM840515VB1</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>payments[].payer_account_number</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>El número de cuenta bancaria del emisor del pago.</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>13343663245699</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>payments[].payer_bank_name</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>La institución bancaria que fue utilizada por el emisor del pago.</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>CITI BANAMEX</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>payments[].related_documents</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Una lista de todas las facturas diferidas relacionadas afectadas por el pago.</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr"/>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>payments[].related_documents[].invoice_identification</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>El ID único de la institución fiscal para la factura diferida relacionada.</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>7EE015F3-6311-11EA-B02A-00155D014007</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
           <t>payments[].related_documents[].currency</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>La moneda de la factura relacionada. Por ejemplo:
 - 🇧🇷 BRL (Real Brasileño)
@@ -34871,236 +35089,14 @@
 Tenga en cuenta que pueden devolverse otras monedas además de las enumeradas anteriormente.</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>MXN</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>payments[].related_documents[].payment_method</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>El método de pago de la factura relacionada.</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>PPD</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>payments[].related_documents[].partiality_number</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>El número de cuota de pago.</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>payments[].related_documents[].previous_balance</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>El monto de la factura antes del pago.</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>18877.84</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>payments[].related_documents[].amount_paid</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>El monto pagado en esta cuota.</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>8000</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>payments[].related_documents[].outstanding_balance</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>El monto restante por pagar.</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>10877.84</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>payroll</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Detalles sobre el pago de nómina. Solo aplicable para facturas de nómina.</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr"/>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
@@ -35120,29 +35116,25 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>payroll.days</t>
+          <t>payments[].related_documents[].payment_method</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>El número de días cubiertos por el pago.</t>
+          <t>El método de pago de la factura relacionada.</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>PPD</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -35159,256 +35151,252 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>payments[].related_documents[].partiality_number</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>El número de cuota de pago.</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>payments[].related_documents[].previous_balance</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>El monto de la factura antes del pago.</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>18877.84</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>payments[].related_documents[].amount_paid</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>El monto pagado en esta cuota.</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>payments[].related_documents[].outstanding_balance</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>El monto restante por pagar.</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>10877.84</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>payroll</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Detalles sobre el pago de nómina. Solo aplicable para facturas de nómina.</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr"/>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>payroll.days</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>El número de días cubiertos por el pago.</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
           <t>payroll.type</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>El tipo de nómina, según lo definido por la entidad legal del país.
 - 🇲🇽 México &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-type" target="_blank"&gt;Artículo de referencia del catálogo SAT&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr"/>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>payroll.amount</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>El monto total del pago de nómina.</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>20400.1</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>payroll.version</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>La versión del objeto de nómina.</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>payroll.date_from</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>La fecha de inicio del período de pago, en formato `YYYY-MM-DD`.</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>2018-07-01</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>payroll.date_to</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>La fecha de finalización del período de pago, en formato `YYYY-MM-DD`.</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>2018-07-31</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>payroll.collected_at</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>La marca de tiempo ISO-8601 cuando se recopiló el punto de datos.</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>2022-02-09T08:45:50.406032Z</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>date-time</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>payroll.payment_date</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>La fecha de pago, en formato `YYYY-MM-DD`.</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>2018-07-16</t>
-        </is>
-      </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
+      <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -35416,7 +35404,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -35425,10 +35413,240 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>payroll.amount</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>El monto total del pago de nómina.</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>20400.1</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>payroll.version</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>La versión del objeto de nómina.</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>payroll.date_from</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>La fecha de inicio del período de pago, en formato `YYYY-MM-DD`.</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>payroll.date_to</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>La fecha de finalización del período de pago, en formato `YYYY-MM-DD`.</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>2018-07-31</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>payroll.collected_at</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>La marca de tiempo ISO-8601 cuando se recopiló el punto de datos.</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-09T08:45:50.406032Z</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>payroll.payment_date</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>La fecha de pago, en formato `YYYY-MM-DD`.</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>2018-07-16</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
           <t>payroll.periodicity</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Con qué frecuencia se realiza el pago de nómina.
 Para el SAT de México, devolvemos uno de los siguientes valores:
@@ -35445,223 +35663,9 @@
   - `OTHER_PERIODICITY`</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>MONTHLY</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr"/>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>DAILY, WEEKLY, TENTH_DAY, FOURTEENTH_DAY, FIFTEENTH_DAY, MONTHLY, BIMONTHLY, PER_TASK, COMMISSION, ONE_OFF, OTHER_PERIODICITY, null</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>payroll.earnings_breakdown</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Un desglose de las ganancias para el pago de nómina.</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr"/>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr"/>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>payroll.earnings_breakdown[].type</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>El tipo de ingreso. Para ver una lista completa de los valores posibles, por favor consulta la &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-earnings-breakdown-type" target="_blank"&gt;tabla de tipos de desglose de ingresos de nómina&lt;/a&gt;.</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>CHRISTMAS_BONUS</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>payroll.earnings_breakdown[].taxable_amount</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>La cantidad de ingresos que es imponible.</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>payroll.earnings_breakdown[].vat_free_amount</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>El monto del ingreso que no está sujeto a IVA.</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>payroll.tax_deductions</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Un desglose de las deducciones fiscales en el pago de nómina.</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr"/>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr"/>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr"/>
-      <c r="I110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>payroll.tax_deductions[].type</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>El tipo de deducción fiscal. Para ver una lista completa de los valores posibles, por favor consulta la &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-tax-deductions-type" target="_blank"&gt;tabla de tipos de deducciones fiscales de nómina&lt;/a&gt;.</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>UNION_FEES</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -35680,35 +35684,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>DAILY, WEEKLY, TENTH_DAY, FOURTEENTH_DAY, FIFTEENTH_DAY, MONTHLY, BIMONTHLY, PER_TASK, COMMISSION, ONE_OFF, OTHER_PERIODICITY, null</t>
+        </is>
+      </c>
       <c r="I111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>payroll.tax_deductions[].amount</t>
+          <t>payroll.earnings_breakdown</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>El monto de la deducción fiscal.</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
-      </c>
+          <t>Un desglose de las ganancias para el pago de nómina.</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr"/>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -35716,7 +35716,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr"/>
@@ -35725,18 +35725,22 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>payroll.other_payments</t>
+          <t>payroll.earnings_breakdown[].type</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Un desglose de otros pagos para la nómina.</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr"/>
+          <t>El tipo de ingreso. Para ver una lista completa de los valores posibles, por favor consulta la &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-earnings-breakdown-type" target="_blank"&gt;tabla de tipos de desglose de ingresos de nómina&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>CHRISTMAS_BONUS</t>
+        </is>
+      </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
@@ -35756,25 +35760,29 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>payroll.other_payments[].type</t>
+          <t>payroll.earnings_breakdown[].taxable_amount</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>El tipo de otro pago. Para ver una lista completa de los valores posibles, consulte la &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-other-payments-type" target="_blank"&gt;tabla de tipos de otros pagos de nómina&lt;/a&gt;.</t>
+          <t>La cantidad de ingresos que es imponible.</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>EMPLOYMENT_SUBSIDY</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -35782,7 +35790,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr"/>
@@ -35791,17 +35799,17 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>payroll.other_payments[].amount</t>
+          <t>payroll.earnings_breakdown[].vat_free_amount</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>El monto del otro pago.</t>
+          <t>El monto del ingreso que no está sujeto a IVA.</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -35830,22 +35838,18 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>folio</t>
+          <t>payroll.tax_deductions</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>El número de control interno que el contribuyente asigna a la factura.</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>Un desglose de las deducciones fiscales en el pago de nómina.</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr"/>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -35865,17 +35869,17 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>export_type</t>
+          <t>payroll.tax_deductions[].type</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>El tipo de exportación de la factura, según lo definido por la entidad legal en el país. Para más información, consulta nuestro &lt;a href="https://developers.belvo.com/docs/sat-catalogs#export-type" target="_blank"&gt;artículo de referencia del catálogo SAT&lt;/a&gt;.</t>
+          <t>El tipo de deducción fiscal. Para ver una lista completa de los valores posibles, por favor consulta la &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-tax-deductions-type" target="_blank"&gt;tabla de tipos de deducciones fiscales de nómina&lt;/a&gt;.</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>UNION_FEES</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -35900,21 +35904,29 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>xml</t>
+          <t>payroll.tax_deductions[].amount</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>XML del documento de factura.</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr"/>
+          <t>El monto de la deducción fiscal.</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -35922,7 +35934,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr"/>
@@ -35931,18 +35943,18 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>payroll.other_payments</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Objeto que contiene información sobre cualquier advertencia relacionada con esta factura.</t>
+          <t>Un desglose de otros pagos para la nómina.</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr"/>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
@@ -35962,10 +35974,251 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>payroll.other_payments[].type</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>El tipo de otro pago. Para ver una lista completa de los valores posibles, consulte la &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-other-payments-type" target="_blank"&gt;tabla de tipos de otros pagos de nómina&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>EMPLOYMENT_SUBSIDY</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>payroll.other_payments[].amount</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>El monto del otro pago.</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>folio</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>El número de control interno que el contribuyente asigna a la factura.</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>La serie de la factura, según lo definido por el contribuyente. Este es un campo opcional utilizado para agrupar facturas.</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>export_type</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>El tipo de exportación de la factura, según lo definido por la entidad legal en el país. Para más información, consulta nuestro &lt;a href="https://developers.belvo.com/docs/sat-catalogs#export-type" target="_blank"&gt;artículo de referencia del catálogo SAT&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>xml</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>XML del documento de factura.</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr"/>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Objeto que contiene información sobre cualquier advertencia relacionada con esta factura.</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr"/>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
           <t>warnings.code</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>El código de advertencia. Puede ser uno de:
   - `sat_xml_limit_reached`
@@ -35973,37 +36226,37 @@
   - `null`</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
         <is>
           <t>sat_xml_limit_reached</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr"/>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>warnings.message</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>La descripción de la advertencia.
 El mensaje dependerá del código de advertencia:
@@ -36013,7 +36266,7 @@
 No está disponible la descarga de detalles de facturas. El portal del SAT generó un error 503.</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The daily limit for XML downloads set by SAT was reached so this invoice
 might be missing data. Please check https://tinyurl.com/yydzhy5d for more
@@ -36021,88 +36274,88 @@
 </t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr"/>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr"/>
-      <c r="I121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>sender_blacklist_status</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>*Este campo ha sido desaprobado. Para obtener más información sobre Belvo y la desaprobación, consulte nuestra explicación de Campos desaprobados.*
 Por favor, use `sender_tax_fraud_status` en su lugar.</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr"/>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr"/>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr"/>
-      <c r="I122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr"/>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>receiver_blacklist_status</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>*Este campo ha sido desaprobado. Para obtener más información sobre Belvo y la desaprobación, consulte nuestra explicación de Campos desaprobados.*
 Por favor, use `receiver_tax_fraud_status` en su lugar.</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr"/>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr"/>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr"/>
-      <c r="I123" s="2" t="inlineStr"/>
+      <c r="C130" s="2" t="inlineStr"/>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data_dictionaries/es/Belvo_Data_Dictionary_es.xlsx
+++ b/data_dictionaries/es/Belvo_Data_Dictionary_es.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -871,14 +871,18 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>form_fields</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr"/>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Este campo está **obsoleto** y se eliminará en una versión futura. Por favor, utilice el campo `id` en su lugar, que es el identificador único para la institución.</t>
+        </is>
+      </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -889,7 +893,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -898,22 +902,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].name</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>El campo de nombre de usuario, contraseña o tipo de nombre de usuario.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>username</t>
-        </is>
-      </c>
+          <t>form_fields</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -933,17 +929,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].type</t>
+          <t>form_fields[].name</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>El tipo de entrada para el campo del formulario. Por ejemplo, string.</t>
+          <t>El campo de nombre de usuario, contraseña o tipo de nombre de usuario.</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>username</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -968,10 +964,45 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>form_fields[].type</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>El tipo de entrada para el campo del formulario. Por ejemplo, string.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>form_fields[].label</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>La etiqueta del campo del formulario. Por ejemplo:
 - Client number
@@ -979,44 +1010,9 @@
 - Document</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Client number</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>form_fields[].validation</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>El tipo de validación de entrada utilizada para el campo.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>^.{1,}$</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1041,17 +1037,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].placeholder</t>
+          <t>form_fields[].validation</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>El texto del marcador de posición en el campo del formulario.</t>
+          <t>El tipo de validación de entrada utilizada para el campo.</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ABC333333A33</t>
+          <t>^.{1,}$</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1076,17 +1072,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].validation_message</t>
+          <t>form_fields[].placeholder</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>El mensaje que se muestra cuando se proporciona una entrada no válida en el campo del formulario.</t>
+          <t>El texto del marcador de posición en el campo del formulario.</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Invalid client number</t>
+          <t>ABC333333A33</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1111,18 +1107,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].values</t>
+          <t>form_fields[].validation_message</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Si el campo del formulario es para documentos, la institución puede requerir información adicional sobre el tipo de documento.</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr"/>
+          <t>El mensaje que se muestra cuando se proporciona una entrada no válida en el campo del formulario.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Invalid client number</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1142,22 +1142,18 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].values[].code</t>
+          <t>form_fields[].values</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>El código del documento.</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
+          <t>Si el campo del formulario es para documentos, la institución puede requerir información adicional sobre el tipo de documento.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1177,10 +1173,45 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>form_fields[].values[].code</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>El código del documento.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>form_fields[].values[].label</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>La etiqueta para el campo. Por ejemplo:
 - Cédula de Ciudadanía
@@ -1188,44 +1219,9 @@
 - Pasaporte</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Cédula de Ciudadanía</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>form_fields[].values[].validation</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>El tipo de validación de entrada utilizada para el campo.</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>^.{1,}$</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1250,17 +1246,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].values[].validation_message</t>
+          <t>form_fields[].values[].validation</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>El mensaje que se muestra cuando se proporciona una entrada no válida en el campo del formulario.</t>
+          <t>El tipo de validación de entrada utilizada para el campo.</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Invalid document number</t>
+          <t>^.{1,}$</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1285,17 +1281,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].values[].placeholder</t>
+          <t>form_fields[].values[].validation_message</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>El texto del marcador de posición en el campo del formulario.</t>
+          <t>El mensaje que se muestra cuando se proporciona una entrada no válida en el campo del formulario.</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>DEF4444908M22</t>
+          <t>Invalid document number</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1320,55 +1316,55 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>form_fields[].values[].placeholder</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>El texto del marcador de posición en el campo del formulario.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>DEF4444908M22</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>features</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Las características que la institución admite. Si la institución no tiene características especiales, entonces Belvo devuelve un array vacío.
 Aquí hay una lista de las características disponibles:
 - `token_required` indica que la institución puede requerir un token durante la creación del enlace o al realizar cualquier otra solicitud.</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr"/>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>array</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>features[].name</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>El nombre de la característica.</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>token_required</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1388,17 +1384,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>features[].description</t>
+          <t>features[].name</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>La descripción de la característica.</t>
+          <t>El nombre de la característica.</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>The institution may require a token during link creation or login</t>
+          <t>token_required</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1423,10 +1419,45 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>features[].description</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>La descripción de la característica.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>The institution may require a token during link creation or login</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>resources</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Una lista de recursos de Belvo que puedes usar con la institución. Esta lista incluye uno o más de los siguientes recursos:
   - `ACCOUNTS`
@@ -1449,85 +1480,46 @@
   - `TAX_STATUS`</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>["ACCOUNTS", "BALANCES", "INCOMES", "OWNERS", "RECURRING_EXPENSES", "RISK_INSIGHTS", "TRANSACTIONS"]</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>array</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>integration_type</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>El tipo de tecnología utilizada para acceder a la institución. Devolvemos uno de los siguientes valores:
 - `credentials`: Utiliza la tecnología de scraping de Belvo, combinada con las credenciales del usuario, para realizar solicitudes.
 - `openfinance`: Utiliza la API de open finance del banco para realizar solicitudes.</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>credentials</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>credentials, openfinance</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Indica si la integración de Belvo con la institución está actualmente activa (`healthy`) o en mantenimiento (`down`).</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>healthy</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1548,7 +1540,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>healthy, down</t>
+          <t>credentials, openfinance</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1556,18 +1548,22 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>openbanking_information</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Información sobre la institución en el entorno de Open Finance.</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr"/>
+          <t>Indica si la integración de Belvo con la institución está actualmente activa (`healthy`) o en mantenimiento (`down`).</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1578,31 +1574,31 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>healthy, down</t>
+        </is>
+      </c>
       <c r="I31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>openbanking_information.description</t>
+          <t>openbanking_information</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Una breve descripción de la institución en el entorno de Open Finance. Extraído del listado de instituciones reguladas por Open Finance.</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>A 1ss Bank é uma fintech fundada em janeiro de 2020, com a missão de ajudar empresas com grandes ecossistemas a se tornarem fintechs, integrando e automatizando seus processos financeiros através de APIs e plataforma white-label.</t>
-        </is>
-      </c>
+          <t>Información sobre la institución en el entorno de Open Finance.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>object</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1622,22 +1618,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>openbanking_information.participants</t>
+          <t>openbanking_information.description</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Lista de servidores de marcas disponibles de la institución en Open Finance. Extraído de la lista de instituciones reguladas por Open Finance.</t>
+          <t>Una breve descripción de la institución en el entorno de Open Finance. Extraído del listado de instituciones reguladas por Open Finance.</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>["1ss Bank"]</t>
+          <t>A 1ss Bank é uma fintech fundada em janeiro de 2020, com a missão de ajudar empresas com grandes ecossistemas a se tornarem fintechs, integrando e automatizando seus processos financeiros através de APIs e plataforma white-label.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1657,29 +1653,25 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>openbanking_information.authorization_server_id</t>
+          <t>openbanking_information.participants</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>El ID del servidor de autorización (UUID) de la institución en el Entorno de Finanzas Abiertas.</t>
+          <t>Lista de servidores de marcas disponibles de la institución en Open Finance. Extraído de la lista de instituciones reguladas por Open Finance.</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>aa18fcd3-2f0b-40b1-87db-8930b10b78b1</t>
+          <t>["1ss Bank"]</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -1692,6 +1684,45 @@
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>openbanking_information.authorization_server_id</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>El ID del servidor de autorización (UUID) de la institución en el Entorno de Finanzas Abiertas.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>aa18fcd3-2f0b-40b1-87db-8930b10b78b1</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -47569,7 +47600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -47781,17 +47812,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>expired_at</t>
+          <t>institution_display_name</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>La marca de tiempo ISO-8601 cuando el consentimiento expirará. En el caso de que `undefined_consent_expiration` sea `true`, este campo será `null`.</t>
+          <t>El nombre para mostrar de la institución bancaria a la que está relacionado el consentimiento.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2021-02-27T13:01:41.941Z</t>
+          <t>Mock Bank</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -47799,11 +47830,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>date-time</t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -47820,22 +47847,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>undefined_consent_expiration</t>
+          <t>institution_icon_logo</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Indique si el consentimiento es por un período indefinido, es decir, que no hay vencimiento para el consentimiento.</t>
+          <t>La URL del logotipo de la institución bancaria.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>https://assets.belvo.io/institutions/mockbank/logo.svg</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -47855,17 +47882,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>belvo_organization_name</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>La marca de tiempo ISO-8601 de cuando se creó el punto de datos en la base de datos de Belvo.</t>
+          <t>El nombre registrado en Belvo de la organización que creó el enlace.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2022-02-09T08:45:50.406032Z</t>
+          <t>ACME Corporation</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -47873,11 +47900,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>date-time</t>
-        </is>
-      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -47894,10 +47917,237 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>link_id</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>El ID de enlace de Belvo al que pertenece el consentimiento.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2e5d2c5e-6b3a-4b5c-8d1e-9f0a1b2c3d4e</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>user_name</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>El nombre proporcionado en `consent.identification_info.name` durante la solicitud inicial del Widget Access Token.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Jack White</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>expired_at</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>La marca de tiempo ISO-8601 cuando el consentimiento expirará. En el caso de que `undefined_consent_expiration` sea `true`, este campo será `null`.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2021-02-27T13:01:41.941Z</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>undefined_consent_expiration</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Indique si el consentimiento es por un período indefinido, es decir, que no hay vencimiento para el consentimiento.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>consent_duration</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>La duración del consentimiento en días. En el caso de que `undefined_consent_expiration` sea `true`, este campo será `null`.
+Valores posibles:
+- `92` (3 meses)
+- `183` (6 meses)
+- `275` (9 meses)
+- `366` (12 meses)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>La marca de tiempo ISO-8601 de cuando se creó el punto de datos en la base de datos de Belvo.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-09T08:45:50.406032Z</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>El estado del consentimiento en la red de finanzas abiertas. Puede ser:
   - `AUTHORISED`: El consentimiento sigue siendo válido para su uso hasta la fecha de `expired_at`.
@@ -47908,224 +48158,14 @@
   - `null`</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>AUTHORISED</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>AUTHORISED, AWAITING_AUTHORISATION_CONFIRMATION, AWAITING_AUTHORISATION, REJECTED, EXPIRED, None</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>permissions</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Detalles sobre los permisos adjuntos al consentimiento.</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>permissions.ACCOUNTS</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Una lista de permisos de banca abierta relacionados con el acceso a la información de la cuenta.</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>["ACCOUNTS_OVERDRAFT_LIMITS_READ", "ACCOUNTS_READ", "ACCOUNTS_TRANSACTIONS_READ", "ACCOUNTS_BALANCES_READ"]</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>permissions.CREDIT_CARDS</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Una lista de permisos de banca abierta relacionados con el acceso a la información de tarjetas de crédito.</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>["CREDIT_CARDS_ACCOUNTS_LIMITS_READ", "CREDIT_CARDS_ACCOUNTS_BILLS_READ", "CREDIT_CARDS_ACCOUNTS_TRANSACTIONS_READ", "CREDIT_CARDS_ACCOUNTS_BILLS_TRANSACTIONS_READ", "CREDIT_CARDS_ACCOUNTS_READ"]</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>permissions.CREDIT_OPERATIONS</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Una lista de permisos de banca abierta relacionados con el acceso a la información de productos de crédito.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>["LOANS_READ", "LOANS_WARRANTIES_READ", "LOANS_SCHEDULED_INSTALMENTS_READ", "LOANS_PAYMENTS_READ", "FINANCINGS_READ", "FINANCINGS_WARRANTIES_READ", "FINANCINGS_SCHEDULED_INSTALMENTS_READ", "FINANCINGS_PAYMENTS_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_WARRANTIES_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_SCHEDULED_INSTALMENTS_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_PAYMENTS_READ", "INVOICE_FINANCINGS_READ", "INVOICE_FINANCINGS_WARRANTIES_READ", "INVOICE_FINANCINGS_SCHEDULED_INSTALMENTS_READ", "INVOICE_FINANCINGS_PAYMENTS_READ"]</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>permissions.REGISTER</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Una lista de permisos de banca abierta relacionados con el acceso a información personal.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>["CUSTOMERS_PERSONAL_IDENTIFICATIONS_READ", "CUSTOMERS_PERSONAL_ADITTIONALINFO_READ"]</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>permissions.RESOURCES</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Una lista de permisos funcionales necesarios para interactuar con los permisos.</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>["RESOURCES_READ"]</t>
-        </is>
-      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -48136,11 +48176,256 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>AUTHORISED, AWAITING_AUTHORISATION_CONFIRMATION, AWAITING_AUTHORISATION, REJECTED, EXPIRED, None</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>permissions</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Detalles sobre los permisos adjuntos al consentimiento.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>permissions.ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Una lista de permisos de banca abierta relacionados con el acceso a la información de la cuenta.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>["ACCOUNTS_OVERDRAFT_LIMITS_READ", "ACCOUNTS_READ", "ACCOUNTS_TRANSACTIONS_READ", "ACCOUNTS_BALANCES_READ"]</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>permissions.CREDIT_CARDS</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Una lista de permisos de banca abierta relacionados con el acceso a la información de tarjetas de crédito.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>["CREDIT_CARDS_ACCOUNTS_LIMITS_READ", "CREDIT_CARDS_ACCOUNTS_BILLS_READ", "CREDIT_CARDS_ACCOUNTS_TRANSACTIONS_READ", "CREDIT_CARDS_ACCOUNTS_BILLS_TRANSACTIONS_READ", "CREDIT_CARDS_ACCOUNTS_READ"]</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>permissions.CREDIT_OPERATIONS</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Una lista de permisos de banca abierta relacionados con el acceso a la información de productos de crédito.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>["LOANS_READ", "LOANS_WARRANTIES_READ", "LOANS_SCHEDULED_INSTALMENTS_READ", "LOANS_PAYMENTS_READ", "FINANCINGS_READ", "FINANCINGS_WARRANTIES_READ", "FINANCINGS_SCHEDULED_INSTALMENTS_READ", "FINANCINGS_PAYMENTS_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_WARRANTIES_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_SCHEDULED_INSTALMENTS_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_PAYMENTS_READ", "INVOICE_FINANCINGS_READ", "INVOICE_FINANCINGS_WARRANTIES_READ", "INVOICE_FINANCINGS_SCHEDULED_INSTALMENTS_READ", "INVOICE_FINANCINGS_PAYMENTS_READ"]</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>permissions.REGISTER</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Una lista de permisos de banca abierta relacionados con el acceso a información personal.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>["CUSTOMERS_PERSONAL_IDENTIFICATIONS_READ", "CUSTOMERS_PERSONAL_ADITTIONALINFO_READ"]</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>permissions.RESOURCES</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Una lista de permisos funcionales necesarios para interactuar con los permisos.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>["RESOURCES_READ"]</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>permissions.INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Una lista de permisos de banca abierta relacionados con el acceso a información de inversiones.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>["BANK_FIXED_INCOMES_READ", "CREDIT_FIXED_INCOMES_READ", "FUNDS_READ", "VARIABLE_INCOMES_READ", "TREASURE_TITLES_READ"]</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data_dictionaries/es/Belvo_Data_Dictionary_es.xlsx
+++ b/data_dictionaries/es/Belvo_Data_Dictionary_es.xlsx
@@ -11259,7 +11259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -11518,22 +11518,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>internal_identification</t>
+          <t>days_since_extraction</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ID único para el usuario según la institución. Para IMSS e ISSSTE México, este es el CURP.</t>
+          <t>El número de días que han pasado desde que los datos de empleo fueron extraídos originalmente de la institución.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>BLPM951331IONVGR54</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -11553,18 +11553,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>personal_data</t>
+          <t>internal_identification</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Detalles sobre la información personal del individuo.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
+          <t>ID único para el usuario según la institución. Para IMSS e ISSSTE México, este es el CURP.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>BLPM951331IONVGR54</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -11584,22 +11588,18 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>personal_data.official_name</t>
+          <t>personal_data</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>El nombre legal del individuo.</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Bruce Banner del Torro</t>
-        </is>
-      </c>
+          <t>Detalles sobre la información personal del individuo.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>object</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -11619,17 +11619,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>personal_data.first_name</t>
+          <t>personal_data.official_name</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>El primer nombre del individuo.</t>
+          <t>El nombre legal del individuo.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Bruce</t>
+          <t>Bruce Banner del Torro</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -11654,17 +11654,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>personal_data.last_name</t>
+          <t>personal_data.first_name</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>El apellido del individuo.</t>
+          <t>El primer nombre del individuo.</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Banner del Torro</t>
+          <t>Bruce</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -11689,17 +11689,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>personal_data.birth_date</t>
+          <t>personal_data.last_name</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>La fecha de nacimiento del individuo, en formato `YYYY-MM-DD`.</t>
+          <t>El apellido del individuo.</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2022-02-09</t>
+          <t>Banner del Torro</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -11707,11 +11707,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -11728,21 +11724,29 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>personal_data.entitlements</t>
+          <t>personal_data.birth_date</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Detalles sobre los beneficios a los que tiene derecho el individuo.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
+          <t>La fecha de nacimiento del individuo, en formato `YYYY-MM-DD`.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-09</t>
+        </is>
+      </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -11750,7 +11754,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -11759,22 +11763,18 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>personal_data.entitlements.entitled_to_health_insurance</t>
+          <t>personal_data.entitlements</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Indica si el individuo tiene derecho o no a un seguro de salud.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>Detalles sobre los beneficios a los que tiene derecho el individuo.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>object</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -11794,12 +11794,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>personal_data.entitlements.entitled_to_company_benefits</t>
+          <t>personal_data.entitlements.entitled_to_health_insurance</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Indica si el individuo tiene derecho o no a beneficios de la empresa.</t>
+          <t>Indica si el individuo tiene derecho o no a un seguro de salud.</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -11829,25 +11829,25 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>personal_data.entitlements.valid_until</t>
+          <t>personal_data.entitlements.entitled_to_company_benefits</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Fecha hasta la cual el individuo está cubierto por el seguro de salud y/o beneficios de la empresa. Si es `null`, el empleado está trabajando actualmente y no se requiere una fecha de finalización.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
+          <t>Indica si el individuo tiene derecho o no a beneficios de la empresa.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -11864,10 +11864,45 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>personal_data.entitlements.valid_until</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Fecha hasta la cual el individuo está cubierto por el seguro de salud y/o beneficios de la empresa. Si es `null`, el empleado está trabajando actualmente y no se requiere una fecha de finalización.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>personal_data.entitlements.status</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Indica el estado laboral del individuo. Devolvemos una de las siguientes respuestas:
   - `EMPLOYED`
@@ -11876,49 +11911,14 @@
   - `null`</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>EMPLOYED</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>EMPLOYED, RETIRED, UNEMPLOYED, null</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>personal_data.document_ids</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Detalles sobre los documentos de identificación del individuo.</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -11932,16 +11932,51 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>EMPLOYED, RETIRED, UNEMPLOYED, null</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>personal_data.document_ids</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Detalles sobre los documentos de identificación del individuo.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>personal_data.document_ids[].document_type</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>El tipo de documento relacionado con el individuo. Devolvemos uno de los siguientes valores:
   - `NSS`
@@ -11949,48 +11984,9 @@
   - `RFC`</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>NSS</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>NSS, CURP, RFC</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>personal_data.document_ids[].document_number</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>El número del documento de identificación (como una cadena).</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>10277663582</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -12009,23 +12005,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>NSS, CURP, RFC</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>personal_data.email</t>
+          <t>personal_data.document_ids[].document_number</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>La dirección de correo electrónico del individuo.</t>
+          <t>El número del documento de identificación (como una cadena).</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>bruce.banner@avengers.com</t>
+          <t>10277663582</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -12050,61 +12050,57 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>personal_data.email</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>La dirección de correo electrónico del individuo.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>bruce.banner@avengers.com</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>social_security_summary</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Detalles sobre las contribuciones al seguro social del individuo, de acuerdo con el IMSS.
 &gt;**Nota**: Para ISSSTE México, este valor devolverá `null`.</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>social_security_summary.weeks_redeemed</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Número de semanas que el individuo necesitó retirar de su pensión.</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
+      <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12121,12 +12117,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>social_security_summary.weeks_reinstated</t>
+          <t>social_security_summary.weeks_redeemed</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Número de semanas que el individuo ha vuelto a cotizar en su pensión (*AFORE*), después de haberlas retirado previamente.</t>
+          <t>Número de semanas que el individuo necesitó retirar de su pensión.</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -12160,17 +12156,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>social_security_summary.weeks_contributed</t>
+          <t>social_security_summary.weeks_reinstated</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Número de semanas que el individuo ha contribuido a su seguridad social, basado en el número de semanas que el individuo ha trabajado según el IMSS.</t>
+          <t>Número de semanas que el individuo ha vuelto a cotizar en su pensión (*AFORE*), después de haberlas retirado previamente.</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -12199,21 +12195,29 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>employment_records</t>
+          <t>social_security_summary.weeks_contributed</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Detalles sobre el historial laboral del individuo.</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr"/>
+          <t>Número de semanas que el individuo ha contribuido a su seguridad social, basado en el número de semanas que el individuo ha trabajado según el IMSS.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12221,7 +12225,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -12230,29 +12234,21 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>employment_records[].collected_at</t>
+          <t>employment_records</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>La marca de tiempo ISO-8601 cuando se recopiló el punto de datos.</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>2020-04-23T21:32:55.336854+00:00</t>
-        </is>
-      </c>
+          <t>Detalles sobre el historial laboral del individuo.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>date-time</t>
-        </is>
-      </c>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12269,101 +12265,101 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>employment_records[].collected_at</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>La marca de tiempo ISO-8601 cuando se recopiló el punto de datos.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2020-04-23T21:32:55.336854+00:00</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>employment_records[].employer</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>El nombre oficial del empleador.
 &gt;**Nota**: Para ISSSTE México, este es el nombre oficial de la entidad junto con la entidad responsable de gestionar la información del empleado, separados por un punto y coma (`;`). Por ejemplo: SECRETARIA DE EDUCACION PUBLICA (SEP);SECRETARIA DE EDUCACION PUBLICA (SEP).</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Batman Enterprises CDMX</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>employment_records[].employer_id</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>El ID oficial del empleador, según el país.
 &gt;**Nota**: Para ISSSTE México, este valor devolverá `null`.</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>780-BAT-88769-CDMX</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>employment_records[].start_date</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Fecha de inicio del empleo, en formato `YYYY-MM-DD`.</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>2019-10-10</t>
-        </is>
-      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
+      <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12371,7 +12367,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -12380,69 +12376,69 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>employment_records[].start_date</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Fecha de inicio del empleo, en formato `YYYY-MM-DD`.</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>2019-10-10</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>employment_records[].end_date</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Fecha en que finalizó el empleo, en formato `YYYY-MM-DD`.
 &gt;**Nota**: Este campo devolverá `null` para el empleo actual del usuario.</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>2019-12-31</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>employment_records[].weeks_employed</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Número de semanas que el individuo estuvo empleado.</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12450,7 +12446,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -12459,143 +12455,147 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>employment_records[].weeks_employed</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Número de semanas que el individuo estuvo empleado.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
           <t>employment_records[].state</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>En qué estado geográfico estaba empleado el individuo, según el país.
 &gt;**Nota**: Para ISSSTE México, este valor devolverá `null`.</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>DISTRITO FEDERAL</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>employment_records[].most_recent_base_salary</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>El salario base más reciente que la persona ganó.
 - Para el IMSS México, este valor se calcula incluyendo las prestaciones a las que la persona tiene derecho durante todo el año.
 - Para el ISSSTE México, este valor se calcula dividiendo `monthly_salary` entre 30 (días) y excluye las prestaciones de la persona.</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>762.54</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>employment_records[].monthly_salary</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>El salario mensual del individuo, incluyendo cualquier beneficio adicional.
 - Para IMSS México, este valor se calcula incluyendo los beneficios a los que el individuo tiene derecho a lo largo del año.
 - Para ISSSTE México, este valor se calcula excluyendo los beneficios.</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>23193.925</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>employment_records[].currency</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>El código de moneda de tres letras en el que se paga el salario.</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>MXN</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12612,18 +12612,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>employment_records[].employment_status_updates</t>
+          <t>employment_records[].currency</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Detalles sobre cualquier cambio de empleo del individuo.</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr"/>
+          <t>El código de moneda de tres letras en el que se paga el salario.</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -12634,7 +12638,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -12643,10 +12647,41 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>employment_records[].employment_status_updates</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Detalles sobre cualquier cambio de empleo del individuo.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>employment_records[].employment_status_updates[].event</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Para el IMSS en México, este es el evento que causó el cambio en el estado de empleo o salario. Devolvemos uno de los siguientes valores:
   - `DISMISSED_RESIGNED`: El empleado fue despedido o renunció.
@@ -12661,99 +12696,60 @@
   - `DYE_CERTIFICATE`: Indica que la información fue recibida de una institución afiliada, **Dependencia y Entidad (DYE)**.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>HIRED</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>DISMISSED_RESIGNED, SALARY_MODIFICATION, HIRED, VOLUNTARY_CONTRIBUTION, ABSENCE, SICK_LEAVE, NORMAL, BDUTA_CERTIFICATE, DYE_CERTIFICATE</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>employment_records[].employment_status_updates[].base_salary</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>El salario base del individuo, vigente a partir de la `update_date`.
   - Para IMSS México, este valor se calcula incluyendo las prestaciones a las que el individuo tiene derecho durante todo el año.
   - Para ISSSTE México, este valor se calcula excluyendo las prestaciones del individuo.</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>1033.09</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>float</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>employment_records[].employment_status_updates[].update_date</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>La fecha en que ocurrió el evento de empleo, en formato `YYYY-MM-DD`.</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>2021-09-01</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -12772,47 +12768,86 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>employment_records[].employment_status_updates[].update_date</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>La fecha en que ocurrió el evento de empleo, en formato `YYYY-MM-DD`.</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
           <t>employment_scores</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Un array de puntuaciones de `employment_record`. Cada puntuación proporciona una visión sobre la empleabilidad y el potencial de generación de ingresos en un período determinado.
 &gt; **Nota 1**: Este campo solo está disponible para enlaces creados con el IMSS de México. Para otras instituciones, este campo devolverá `null`.
 &gt; **Nota 2**: Este campo devolverá `null` para los registros de empleo recuperados antes del 16-04-2024. Para los registros de empleo generados antes del 16-04-2024, necesitarás hacer una nueva solicitud POST para recuperar los registros de empleo y calcular las puntuaciones.</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>[{"score": 722, "period": 3, "version": "1.0.0"}, {"score": 612, "period": 6, "version": "1.0.0"}, {"score": 570, "period": 12, "version": "1.0.0"}]</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>array</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>employment_scores[].score</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Una puntuación entre 300 y 900 que proporciona una visión sobre la empleabilidad y el potencial de generación de ingresos.
 - Una puntuación baja (más cercana a 300) podría indicar una menor empleabilidad y potencial de generación de ingresos, sugiriendo posibles desafíos para asegurar empleo o alcanzar niveles de ingresos más altos en el futuro.
@@ -12820,86 +12855,51 @@
 La puntuación puede devolver `null` si el individuo no tiene historial laboral.</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>employment_scores[].period</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>El número de meses (en el futuro) para los cuales se calcula la puntuación.
 Por ejemplo, un período de `6` indica que la puntuación se calcula para los próximos `6` meses.
 &gt; **Nota**: Actualmente, Belvo calcula la puntuación para 3, 6 y 12 meses.</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>integer</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>employment_scores[].version</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>La versión de nuestro modelo de puntuación de empleo utilizada para realizar el cálculo.</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>1.0.0</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -12919,18 +12919,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>files</t>
+          <t>employment_scores[].version</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Archivos binarios PDF adicionales relacionados con el empleo del individuo.</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr"/>
+          <t>La versión de nuestro modelo de puntuación de empleo utilizada para realizar el cálculo.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -12941,7 +12945,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -12950,22 +12954,19 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>files[].type</t>
+          <t>salary_estimation</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>El título del documento.</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>ReporteSemanasCotizadas_190123</t>
-        </is>
-      </c>
+          <t>Proporciona una estimación modelada del salario base actual del usuario y su estado de empleo.
+&gt; **Nota**: Este campo solo está disponible para enlaces creados con el IMSS de México. Para otras instituciones (como el ISSSTE), este campo devolverá `null`.</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>object</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -12976,7 +12977,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -12985,37 +12986,212 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>salary_estimation.employment_status_estimate</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>El estado de empleo actual se estima utilizando un registro de empleo con una fecha de informe pasada. Devuelve `"EMPLOYED"` (si el `base_salary_estimate` es mayor que 0) o `"UNEMPLOYED"`.</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>EMPLOYED</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>salary_estimation.base_salary_estimate</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Salario base actual (monto diario) estimado utilizando un registro de empleo con una fecha de informe pasada.</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>salary_estimation.currency</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>El código de moneda de tres letras (ISO-4217). Por ejemplo, `"MXN"`.</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>files</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Archivos binarios PDF adicionales relacionados con el empleo del individuo.</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>files[].type</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>El título del documento.</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>ReporteSemanasCotizadas_190123</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
           <t>files[].value</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>El binario PDF del archivo (como una cadena).
 &gt; **Nota**: En nuestro entorno sandbox, este campo devolverá `null`.</t>
         </is>
       </c>
-      <c r="C47" s="2">
+      <c r="C52" s="2">
         <f>PDF_BINARY=</f>
         <v/>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
